--- a/data/trans_orig/IP07C02-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP07C02-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido correr bien en 2007 (tasa de respuesta: 89,79%)</t>
+          <t>Menores según la frecuencia de haber podido correr bien en 2007 (tasa de respuesta: 89,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15177</t>
+          <t>15828</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25407</t>
+          <t>26089</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63,64%</t>
+          <t>65,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17539</t>
+          <t>17501</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26457</t>
+          <t>26956</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>35876</t>
+          <t>35302</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49428</t>
+          <t>49584</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>47,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>66,07%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12531</t>
+          <t>12332</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22640</t>
+          <t>22720</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>56,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8337</t>
+          <t>7606</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17070</t>
+          <t>17013</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>48,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23611</t>
+          <t>23522</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>37649</t>
+          <t>37581</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>50,08%</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5653</t>
+          <t>4998</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5348</t>
+          <t>4865</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3811</t>
+          <t>2828</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2807</t>
+          <t>3431</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10240</t>
+          <t>10018</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18471</t>
+          <t>17951</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>39,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>71,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9630</t>
+          <t>9137</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18122</t>
+          <t>18105</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>61,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22719</t>
+          <t>22450</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34239</t>
+          <t>34273</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>41,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>62,62%</t>
+          <t>62,68%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6169</t>
+          <t>6512</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14355</t>
+          <t>14485</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>57,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10845</t>
+          <t>10787</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19342</t>
+          <t>19904</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>65,68%</t>
+          <t>67,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>18683</t>
+          <t>19200</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>30424</t>
+          <t>30827</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>55,64%</t>
+          <t>56,38%</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4107</t>
+          <t>4280</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4431</t>
+          <t>3769</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>6,89%</t>
         </is>
       </c>
     </row>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3747</t>
+          <t>3399</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3225</t>
+          <t>3171</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,8%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8856</t>
+          <t>9094</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17562</t>
+          <t>17115</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,69%</t>
+          <t>59,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19485</t>
+          <t>19929</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31308</t>
+          <t>31582</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>61,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31436</t>
+          <t>30736</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>45924</t>
+          <t>46224</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>57,69%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8917</t>
+          <t>8984</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17706</t>
+          <t>17299</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>59,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15124</t>
+          <t>15483</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26657</t>
+          <t>26340</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>51,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>26648</t>
+          <t>26216</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>41250</t>
+          <t>40922</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>51,08%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>736</t>
+          <t>755</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>6094</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7364</t>
+          <t>7151</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2756</t>
+          <t>2797</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>10055</t>
+          <t>10652</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>13,3%</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3634</t>
+          <t>3969</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4179</t>
+          <t>4162</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>670</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5874</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>6,84%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>34698</t>
+          <t>35508</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>50091</t>
+          <t>50040</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>58,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>43650</t>
+          <t>43520</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>57537</t>
+          <t>57768</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>53,84%</t>
+          <t>53,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>71,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>83763</t>
+          <t>82858</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>104183</t>
+          <t>103532</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>50,18%</t>
+          <t>49,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>62,41%</t>
+          <t>62,02%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>30489</t>
+          <t>30593</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>45785</t>
+          <t>45796</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>53,34%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>19873</t>
+          <t>19786</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>33783</t>
+          <t>33575</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>54874</t>
+          <t>54493</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>74874</t>
+          <t>74606</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>44,69%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1175</t>
+          <t>1548</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7179</t>
+          <t>7704</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>666</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6044</t>
+          <t>6584</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3179</t>
+          <t>3098</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>10994</t>
+          <t>11102</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,65%</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4306</t>
+          <t>5335</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4516</t>
+          <t>4379</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -3270,7 +3270,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4054</t>
+          <t>4477</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4360</t>
+          <t>3911</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>22679</t>
+          <t>23047</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>33878</t>
+          <t>33502</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>47,98%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>69,75%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>27094</t>
+          <t>27840</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>40043</t>
+          <t>40504</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>64,01%</t>
+          <t>64,75%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>54545</t>
+          <t>54059</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>70745</t>
+          <t>70910</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>48,88%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>64,12%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>10947</t>
+          <t>10901</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>21132</t>
+          <t>21000</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>43,72%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>20122</t>
+          <t>20045</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>32711</t>
+          <t>32673</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>52,23%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>33888</t>
+          <t>33626</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>50662</t>
+          <t>49834</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>45,06%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4737</t>
+          <t>4793</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2790</t>
+          <t>2799</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>633</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5930</t>
+          <t>6180</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>529</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5278</t>
+          <t>5050</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>4163</t>
+          <t>4276</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1160</t>
+          <t>1150</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>7157</t>
+          <t>7061</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -3952,7 +3952,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3494</t>
+          <t>3499</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3456</t>
+          <t>3700</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>14195</t>
+          <t>13526</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>23571</t>
+          <t>23814</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>62,41%</t>
+          <t>63,05%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>13107</t>
+          <t>13012</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>22343</t>
+          <t>22451</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>70,29%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>28621</t>
+          <t>29803</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>42958</t>
+          <t>43147</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>61,63%</t>
+          <t>61,9%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>12137</t>
+          <t>12073</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>21754</t>
+          <t>21716</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>57,6%</t>
+          <t>57,5%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>8637</t>
+          <t>8562</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>17326</t>
+          <t>17342</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>54,25%</t>
+          <t>54,3%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>23293</t>
+          <t>22975</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>37433</t>
+          <t>35936</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>51,55%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>622</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>5607</t>
+          <t>5874</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4408,7 +4408,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4083</t>
+          <t>4060</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1320</t>
+          <t>1324</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>7711</t>
+          <t>7826</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,23%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>125422</t>
+          <t>124406</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>150912</t>
+          <t>150412</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>46,81%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>56,6%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>151005</t>
+          <t>150517</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>178701</t>
+          <t>177500</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>51,83%</t>
+          <t>51,67%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>60,93%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>282882</t>
+          <t>282184</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>321323</t>
+          <t>323326</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>57,68%</t>
+          <t>58,04%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>98070</t>
+          <t>98908</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>124254</t>
+          <t>124555</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,82 +4952,82 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
+          <t>37,22%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>46,87%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>112994</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>99854</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>127593</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>38,79%</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>34,28%</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>43,8%</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>224252</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>205580</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>244245</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>40,26%</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
           <t>36,9%</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>46,76%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>112994</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>99038</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>126880</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>38,79%</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>34,0%</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>43,55%</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>224252</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>205754</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t>244083</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr">
-        <is>
-          <t>40,26%</t>
-        </is>
-      </c>
-      <c r="V41" s="2" t="inlineStr">
-        <is>
-          <t>36,94%</t>
-        </is>
-      </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>43,82%</t>
+          <t>43,85%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7455</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>19150</t>
+          <t>18543</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>4047</t>
+          <t>4496</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>13446</t>
+          <t>13166</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>13822</t>
+          <t>13699</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>28377</t>
+          <t>28895</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1446</t>
+          <t>1389</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>7830</t>
+          <t>8655</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>7421</t>
+          <t>7429</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>3660</t>
+          <t>3518</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>12281</t>
+          <t>12658</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -5311,12 +5311,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>640</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>6260</t>
+          <t>6097</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5326,12 +5326,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>690</t>
+          <t>673</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>6364</t>
+          <t>5859</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido correr bien en 2012 (tasa de respuesta: 95,62%)</t>
+          <t>Menores según la frecuencia de haber podido correr bien en 2012 (tasa de respuesta: 95,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5740,12 +5740,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7803</t>
+          <t>8084</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17488</t>
+          <t>17818</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5755,12 +5755,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>49,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9942</t>
+          <t>9725</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19209</t>
+          <t>19485</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>56,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20442</t>
+          <t>20036</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33419</t>
+          <t>33971</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>48,22%</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15286</t>
+          <t>14686</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25059</t>
+          <t>24857</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>68,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12511</t>
+          <t>12365</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21788</t>
+          <t>21906</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>36,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>64,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31007</t>
+          <t>30885</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44282</t>
+          <t>44889</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>63,71%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1382</t>
+          <t>1487</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7082</t>
+          <t>8647</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6006,7 +6006,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>4356</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6021,7 +6021,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2174</t>
+          <t>2159</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10073</t>
+          <t>9327</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>13,24%</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3295</t>
+          <t>2757</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2899</t>
+          <t>3493</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -6232,7 +6232,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3650</t>
+          <t>4150</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6247,7 +6247,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3712</t>
+          <t>3553</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9706</t>
+          <t>9311</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18497</t>
+          <t>18885</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>56,73%</t>
+          <t>57,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15743</t>
+          <t>15666</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25047</t>
+          <t>25237</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>44,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>71,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27866</t>
+          <t>27456</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>40847</t>
+          <t>40924</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>60,44%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10290</t>
+          <t>9998</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19284</t>
+          <t>19228</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>59,15%</t>
+          <t>58,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9132</t>
+          <t>8851</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18146</t>
+          <t>18117</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,69%</t>
+          <t>51,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>21920</t>
+          <t>21534</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>34646</t>
+          <t>35183</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>51,17%</t>
+          <t>51,96%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>662</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6259</t>
+          <t>6463</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6688,7 +6688,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3780</t>
+          <t>3823</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6703,7 +6703,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1403</t>
+          <t>1412</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8614</t>
+          <t>8566</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,65%</t>
         </is>
       </c>
     </row>
@@ -6766,7 +6766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3780</t>
+          <t>3422</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4028</t>
+          <t>3421</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6851,7 +6851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3001</t>
+          <t>2687</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6894,7 +6894,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3815</t>
+          <t>2937</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10750</t>
+          <t>10640</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20992</t>
+          <t>20657</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12521</t>
+          <t>11956</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20880</t>
+          <t>21246</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>67,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>24884</t>
+          <t>24719</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39101</t>
+          <t>38107</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>51,24%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19483</t>
+          <t>19705</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29973</t>
+          <t>30084</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>69,73%</t>
+          <t>69,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9202</t>
+          <t>8713</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17521</t>
+          <t>17893</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>57,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>31475</t>
+          <t>32201</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>45701</t>
+          <t>46023</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>61,88%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>501</t>
+          <t>497</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5750</t>
+          <t>5946</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7370,7 +7370,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4854</t>
+          <t>4105</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7385,7 +7385,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1214</t>
+          <t>1209</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7689</t>
+          <t>7547</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7420,7 +7420,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,15%</t>
         </is>
       </c>
     </row>
@@ -7448,7 +7448,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2877</t>
+          <t>3560</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7463,7 +7463,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3218</t>
+          <t>3470</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7533,7 +7533,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24249</t>
+          <t>24350</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>39236</t>
+          <t>38562</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>45,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>44827</t>
+          <t>44845</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>60759</t>
+          <t>60794</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>72233</t>
+          <t>72917</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>95185</t>
+          <t>94196</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>52,21%</t>
+          <t>51,67%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>39483</t>
+          <t>39489</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>54510</t>
+          <t>53925</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>46,69%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>30358</t>
+          <t>30297</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>46083</t>
+          <t>46878</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>47,97%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>74399</t>
+          <t>74927</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>96243</t>
+          <t>97802</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>40,81%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>52,79%</t>
+          <t>53,65%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1807</t>
+          <t>1799</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10065</t>
+          <t>9139</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1751</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8569</t>
+          <t>7961</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4509</t>
+          <t>4206</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>13736</t>
+          <t>14291</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,84%</t>
         </is>
       </c>
     </row>
@@ -8130,7 +8130,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3592</t>
+          <t>3354</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8145,7 +8145,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>626</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5746</t>
+          <t>6079</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8180,7 +8180,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>935</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7691</t>
+          <t>7540</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -8243,7 +8243,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4281</t>
+          <t>3593</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8258,7 +8258,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8278,7 +8278,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3931</t>
+          <t>4073</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>432</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4906</t>
+          <t>5462</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>21432</t>
+          <t>21586</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>35597</t>
+          <t>35932</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>47,7%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>25759</t>
+          <t>24901</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>39454</t>
+          <t>39255</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>54,75%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>51356</t>
+          <t>51644</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>70151</t>
+          <t>70447</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>47,8%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>33476</t>
+          <t>33329</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>47601</t>
+          <t>48103</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>44,44%</t>
+          <t>44,25%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>63,2%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>27764</t>
+          <t>27541</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>41689</t>
+          <t>41510</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>57,85%</t>
+          <t>57,6%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>64758</t>
+          <t>64993</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>84841</t>
+          <t>84638</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>57,43%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2375</t>
+          <t>2475</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>10482</t>
+          <t>10720</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>748</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5957</t>
+          <t>6938</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>4278</t>
+          <t>4253</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>14414</t>
+          <t>13807</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,37%</t>
         </is>
       </c>
     </row>
@@ -8812,7 +8812,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3255</t>
+          <t>3310</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8827,7 +8827,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>4420</t>
+          <t>4419</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>646</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6021</t>
+          <t>5699</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8897,7 +8897,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -8960,7 +8960,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4152</t>
+          <t>4108</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4709</t>
+          <t>5345</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>3288</t>
+          <t>3237</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>9950</t>
+          <t>9991</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>43,82%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>16494</t>
+          <t>16619</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>25696</t>
+          <t>26184</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>47,02%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>74,09%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>21154</t>
+          <t>21327</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>33552</t>
+          <t>33517</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>57,64%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>11232</t>
+          <t>10758</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>18550</t>
+          <t>18060</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>49,26%</t>
+          <t>47,18%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>79,2%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>7246</t>
+          <t>6734</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>16178</t>
+          <t>15732</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>20387</t>
+          <t>20623</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>32768</t>
+          <t>33417</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>56,36%</t>
+          <t>57,47%</t>
         </is>
       </c>
     </row>
@@ -9381,7 +9381,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4843</t>
+          <t>4786</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9416,7 +9416,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4810</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>777</t>
+          <t>801</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>6727</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>12,31%</t>
         </is>
       </c>
     </row>
@@ -9529,7 +9529,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3149</t>
+          <t>2517</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9544,7 +9544,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9564,7 +9564,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>2650</t>
+          <t>3067</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9579,7 +9579,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -9642,7 +9642,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>2539</t>
+          <t>3335</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9657,7 +9657,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9677,7 +9677,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3120</t>
+          <t>3245</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>93974</t>
+          <t>93695</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>121620</t>
+          <t>120914</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>41,05%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>142921</t>
+          <t>144215</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>172062</t>
+          <t>171814</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>47,16%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>56,26%</t>
+          <t>56,18%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>243920</t>
+          <t>246352</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>286595</t>
+          <t>285493</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>47,55%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>149384</t>
+          <t>148639</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>176659</t>
+          <t>176973</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>50,46%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>59,98%</t>
+          <t>60,08%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>113350</t>
+          <t>113963</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>141858</t>
+          <t>142265</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>46,52%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>270305</t>
+          <t>271745</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>310088</t>
+          <t>311072</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>45,26%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>51,81%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>13400</t>
+          <t>13884</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>28051</t>
+          <t>28448</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10073,12 +10073,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>7193</t>
+          <t>7479</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>17253</t>
+          <t>17809</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>23374</t>
+          <t>24031</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>42055</t>
+          <t>41467</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,91%</t>
         </is>
       </c>
     </row>
@@ -10171,12 +10171,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>666</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>6530</t>
+          <t>6266</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10186,12 +10186,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>2175</t>
+          <t>1886</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>9996</t>
+          <t>9573</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>4006</t>
+          <t>3816</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>13631</t>
+          <t>12766</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>431</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>4613</t>
+          <t>4795</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1334</t>
+          <t>1330</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>7674</t>
+          <t>7584</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10339,7 +10339,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>2334</t>
+          <t>2245</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>10120</t>
+          <t>9844</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -10553,7 +10553,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido correr bien en 2016 (tasa de respuesta: 95,67%)</t>
+          <t>Menores según la frecuencia de haber podido correr bien en 2016 (tasa de respuesta: 95,67%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16980</t>
+          <t>16947</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25603</t>
+          <t>25582</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10763,12 +10763,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>52,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>78,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10783,12 +10783,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18052</t>
+          <t>18357</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28302</t>
+          <t>28462</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10798,12 +10798,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>48,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>75,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10818,12 +10818,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>38043</t>
+          <t>38733</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51251</t>
+          <t>51834</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10833,12 +10833,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,31%</t>
+          <t>55,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>74,0%</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>6314</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14654</t>
+          <t>14758</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8134</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17993</t>
+          <t>17832</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>47,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16865</t>
+          <t>16363</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>30049</t>
+          <t>29452</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>42,05%</t>
         </is>
       </c>
     </row>
@@ -10979,7 +10979,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3781</t>
+          <t>4520</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10994,7 +10994,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11014,7 +11014,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4265</t>
+          <t>4305</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11029,7 +11029,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>619</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5053</t>
+          <t>5562</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11064,7 +11064,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,94%</t>
         </is>
       </c>
     </row>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20747</t>
+          <t>21044</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33125</t>
+          <t>32609</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11445,12 +11445,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>42,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>66,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29249</t>
+          <t>29580</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39293</t>
+          <t>39685</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11480,12 +11480,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>61,27%</t>
+          <t>61,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>54134</t>
+          <t>54600</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>69146</t>
+          <t>70184</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11515,12 +11515,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>72,37%</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14592</t>
+          <t>15522</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26784</t>
+          <t>27655</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>54,39%</t>
+          <t>56,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5656</t>
+          <t>5725</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14750</t>
+          <t>14872</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>23841</t>
+          <t>22868</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>38535</t>
+          <t>38220</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>39,41%</t>
         </is>
       </c>
     </row>
@@ -11661,7 +11661,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3682</t>
+          <t>3365</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11676,7 +11676,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4498</t>
+          <t>4392</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11711,7 +11711,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5943</t>
+          <t>5902</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11746,7 +11746,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,09%</t>
         </is>
       </c>
     </row>
@@ -11774,7 +11774,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3762</t>
+          <t>3255</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11789,7 +11789,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5841</t>
+          <t>5272</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>738</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6765</t>
+          <t>6848</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,06%</t>
         </is>
       </c>
     </row>
@@ -12112,12 +12112,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14256</t>
+          <t>14265</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22352</t>
+          <t>22318</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12127,12 +12127,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>51,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>81,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12147,12 +12147,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17631</t>
+          <t>17698</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27953</t>
+          <t>27520</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12162,12 +12162,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>68,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>34670</t>
+          <t>34909</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>48045</t>
+          <t>47965</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12197,12 +12197,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>51,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>71,11%</t>
         </is>
       </c>
     </row>
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3415</t>
+          <t>3802</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10962</t>
+          <t>11310</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12240,12 +12240,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9529</t>
+          <t>9820</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19463</t>
+          <t>19434</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>48,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>15150</t>
+          <t>14963</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>27943</t>
+          <t>27488</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,42%</t>
+          <t>40,75%</t>
         </is>
       </c>
     </row>
@@ -12343,7 +12343,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3629</t>
+          <t>3652</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12358,7 +12358,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>644</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6128</t>
+          <t>5664</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>725</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6507</t>
+          <t>6630</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12428,7 +12428,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,83%</t>
         </is>
       </c>
     </row>
@@ -12491,7 +12491,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2664</t>
+          <t>3295</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12506,7 +12506,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12526,7 +12526,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3255</t>
+          <t>3250</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12541,7 +12541,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -12569,7 +12569,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3939</t>
+          <t>3998</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12584,7 +12584,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12639,7 +12639,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4132</t>
+          <t>3782</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12654,7 +12654,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>55807</t>
+          <t>55859</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>72975</t>
+          <t>72367</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12809,12 +12809,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>50,41%</t>
+          <t>50,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>65,92%</t>
+          <t>65,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>47885</t>
+          <t>48453</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>65318</t>
+          <t>65306</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12844,12 +12844,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>48,53%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>108176</t>
+          <t>108092</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>132839</t>
+          <t>132493</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>51,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>63,44%</t>
+          <t>63,28%</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12907,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>32496</t>
+          <t>32885</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>49128</t>
+          <t>49483</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>44,7%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>29286</t>
+          <t>30037</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>46192</t>
+          <t>45909</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>46,53%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>67374</t>
+          <t>67530</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>91492</t>
+          <t>90932</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>43,43%</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9021</t>
+          <t>9790</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13040,7 +13040,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>675</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7109</t>
+          <t>8162</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13075,7 +13075,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3972</t>
+          <t>3856</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>12550</t>
+          <t>13071</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -13138,7 +13138,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3736</t>
+          <t>3709</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13153,7 +13153,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13173,7 +13173,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3351</t>
+          <t>3340</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13188,7 +13188,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13208,7 +13208,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4394</t>
+          <t>4945</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13223,7 +13223,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -13286,7 +13286,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2860</t>
+          <t>2968</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13301,7 +13301,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13321,7 +13321,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2937</t>
+          <t>3155</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13336,7 +13336,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -13476,12 +13476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>38307</t>
+          <t>37975</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>51994</t>
+          <t>51720</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>51,34%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13511,12 +13511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>32129</t>
+          <t>31163</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>46566</t>
+          <t>45979</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13526,12 +13526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>65,4%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13546,12 +13546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>74361</t>
+          <t>73689</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>94062</t>
+          <t>93363</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>51,54%</t>
+          <t>51,08%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>64,71%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>20643</t>
+          <t>20963</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>34410</t>
+          <t>34961</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>46,52%</t>
+          <t>47,27%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>19529</t>
+          <t>19704</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>32966</t>
+          <t>33872</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>48,18%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>44885</t>
+          <t>44421</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>63835</t>
+          <t>64965</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>45,03%</t>
         </is>
       </c>
     </row>
@@ -13707,7 +13707,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4466</t>
+          <t>4493</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13722,7 +13722,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>7812</t>
+          <t>7979</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2101</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>9345</t>
+          <t>9172</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -13855,7 +13855,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>5349</t>
+          <t>4920</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13870,7 +13870,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13890,7 +13890,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4554</t>
+          <t>4467</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13905,7 +13905,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -13968,7 +13968,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3587</t>
+          <t>4793</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13983,7 +13983,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14003,7 +14003,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4332</t>
+          <t>3707</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14018,7 +14018,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -14158,12 +14158,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>15872</t>
+          <t>15448</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>24929</t>
+          <t>24796</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14173,12 +14173,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>74,73%</t>
+          <t>74,33%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>19805</t>
+          <t>19777</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>29322</t>
+          <t>29532</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>53,3%</t>
+          <t>53,23%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14228,12 +14228,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>37699</t>
+          <t>38187</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>51699</t>
+          <t>51957</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14243,12 +14243,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>54,15%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>73,68%</t>
         </is>
       </c>
     </row>
@@ -14271,12 +14271,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>5100</t>
+          <t>4986</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>12864</t>
+          <t>13166</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14286,12 +14286,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>39,47%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>6277</t>
+          <t>5971</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>15272</t>
+          <t>15475</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14321,12 +14321,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>13534</t>
+          <t>12870</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>25881</t>
+          <t>25175</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>35,7%</t>
         </is>
       </c>
     </row>
@@ -14384,12 +14384,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>686</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>6599</t>
+          <t>6779</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14399,12 +14399,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14424,7 +14424,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3490</t>
+          <t>3688</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14439,7 +14439,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>731</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>8236</t>
+          <t>7981</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,32%</t>
         </is>
       </c>
     </row>
@@ -14502,7 +14502,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3805</t>
+          <t>4200</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14517,7 +14517,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14537,7 +14537,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3688</t>
+          <t>4329</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14552,7 +14552,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14572,7 +14572,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4531</t>
+          <t>5318</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14587,7 +14587,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>7,54%</t>
         </is>
       </c>
     </row>
@@ -14615,7 +14615,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>4038</t>
+          <t>4567</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -14630,7 +14630,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -14650,7 +14650,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>4353</t>
+          <t>3793</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>5410</t>
+          <t>4832</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14700,7 +14700,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>183345</t>
+          <t>182122</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>212929</t>
+          <t>211790</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14855,12 +14855,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>56,01%</t>
+          <t>55,64%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>64,7%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>186163</t>
+          <t>185816</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>216161</t>
+          <t>216546</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>56,19%</t>
+          <t>56,08%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>65,24%</t>
+          <t>65,36%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>378787</t>
+          <t>378992</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>421680</t>
+          <t>419416</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14925,12 +14925,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>57,51%</t>
+          <t>57,54%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>64,02%</t>
+          <t>63,68%</t>
         </is>
       </c>
     </row>
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>100255</t>
+          <t>101685</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>129241</t>
+          <t>130638</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14968,12 +14968,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>96979</t>
+          <t>97746</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>125421</t>
+          <t>126591</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>205342</t>
+          <t>207062</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>245512</t>
+          <t>246536</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15038,12 +15038,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,43%</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>6066</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>17778</t>
+          <t>17266</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>7143</t>
+          <t>6258</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>18413</t>
+          <t>17298</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>14570</t>
+          <t>15180</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>29989</t>
+          <t>29883</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -15179,12 +15179,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>614</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>5605</t>
+          <t>5715</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15199,7 +15199,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>2153</t>
+          <t>2146</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>9483</t>
+          <t>9938</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15234,7 +15234,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>3523</t>
+          <t>3530</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>13144</t>
+          <t>12711</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15264,12 +15264,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -15292,12 +15292,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>614</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>5628</t>
+          <t>5949</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15312,7 +15312,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15327,12 +15327,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>587</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>6008</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15347,7 +15347,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1379</t>
+          <t>1418</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>8026</t>
+          <t>9015</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15377,12 +15377,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
